--- a/Classeur1.xlsx
+++ b/Classeur1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicolas.ngo\Documents\Articles\Article3\Dynamic_Prediction_of_PAF_Poster\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7AE4CFE-1F1A-4A45-8E3A-9ACC26555065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99C7DA4D-0A30-4A00-8652-95B9899C0786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FE358A9D-BEEC-4F7C-88A1-BDCB3B1C2DF3}"/>
   </bookViews>
@@ -5413,6 +5413,328 @@
       </cdr:txBody>
     </cdr:sp>
   </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.65056</cdr:x>
+      <cdr:y>0.32521</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.78563</cdr:x>
+      <cdr:y>0.64172</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="8" name="Ellipse 7">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{637A4054-272E-4B09-80C7-6EBD9D0A4954}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="18899795">
+          <a:off x="5950090" y="2285861"/>
+          <a:ext cx="1921959" cy="1299937"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:schemeClr val="bg2">
+            <a:alpha val="20000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:solidFill>
+            <a:srgbClr val="C00000"/>
+          </a:solidFill>
+        </a:ln>
+      </cdr:spPr>
+      <cdr:style>
+        <a:lnRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </cdr:style>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="fr-FR" sz="1100"/>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.73171</cdr:x>
+      <cdr:y>0.56834</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.98205</cdr:x>
+      <cdr:y>0.83204</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="9" name="Ellipse 8">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C92C0D7D-5DB0-A9AE-0C35-4C09E8ACE747}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="21156957">
+          <a:off x="7042149" y="3451225"/>
+          <a:ext cx="2409264" cy="1601338"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:schemeClr val="bg2">
+            <a:alpha val="20000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:solidFill>
+            <a:srgbClr val="C00000"/>
+          </a:solidFill>
+        </a:ln>
+      </cdr:spPr>
+      <cdr:style>
+        <a:lnRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </cdr:style>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="fr-FR" sz="1100"/>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
 </c:userShapes>
 </file>
 
